--- a/Result/profitability/1618.xlsx
+++ b/Result/profitability/1618.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.01</v>
       </c>
       <c r="M2" t="n">
-        <v>0.99625</v>
+        <v>1.015</v>
       </c>
       <c r="N2" t="n">
-        <v>19.73875</v>
+        <v>20.96375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.85</v>
+        <v>0.89125</v>
       </c>
       <c r="N3" t="n">
-        <v>17.7675</v>
+        <v>19.12</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.39</v>
       </c>
       <c r="M4" t="n">
-        <v>0.77375</v>
+        <v>0.7862500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>15.8325</v>
+        <v>16.64125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.92</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5050000000000001</v>
+        <v>0.5437500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>9.447499999999998</v>
+        <v>11.54375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.04</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3725000000000001</v>
+        <v>0.4125000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>7.67</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,16 +1264,16 @@
         <v>0.29</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2825</v>
+        <v>0.3300000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>6.3675</v>
+        <v>7.8625</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.45</v>
       </c>
       <c r="M8" t="n">
-        <v>0.22</v>
+        <v>0.19</v>
       </c>
       <c r="N8" t="n">
-        <v>5.08625</v>
+        <v>4.84375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1124</v>
+      </c>
+      <c r="D75" t="n">
+        <v>767</v>
+      </c>
+      <c r="E75" t="n">
+        <v>358</v>
+      </c>
+      <c r="F75" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>300</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>26.72%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>26</v>
+      </c>
+      <c r="J75" t="n">
+        <v>326</v>
+      </c>
+      <c r="K75" t="n">
+        <v>256</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.16125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>23.265</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1528662420382165</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.940000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.05749851807943096</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.303921568627451</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.115768463073852</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
